--- a/public/exports-60-250-with-coowners/29189668.xlsx
+++ b/public/exports-60-250-with-coowners/29189668.xlsx
@@ -9214,7 +9214,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
